--- a/results/StudyDetails.xlsx
+++ b/results/StudyDetails.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manjulat/Projects/Araichi/SkinDataAnalysis/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5AE8B1-051E-F54B-8B3C-71A8BF3BF2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00AF491-C611-C246-8498-C9435D9D5DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{25722A3C-8689-2743-954C-0104D0233038}"/>
+    <workbookView xWindow="11560" yWindow="660" windowWidth="22180" windowHeight="16680" activeTab="1" xr2:uid="{25722A3C-8689-2743-954C-0104D0233038}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="180">
   <si>
     <t>Study</t>
   </si>
@@ -68,18 +70,9 @@
     <t>GSE153760</t>
   </si>
   <si>
-    <t>AD1 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19  AD2  AD3  AD4  AD5  AD6  AD7  AD8  HC1  HC2  HC3  HC4  HC5 
-4846 1054 1499 1570 4562 2976  489 1866 2478 1942  943 3803 1819 3222 5628 5104 6246 5555   87  672 2662 2103  668 
- HC6  HC7 
-5455 9737</t>
-  </si>
-  <si>
     <t>GSE180885</t>
   </si>
   <si>
-    <t>53 AD, 14 (Healthy)</t>
-  </si>
-  <si>
     <t>GEO Link</t>
   </si>
   <si>
@@ -108,13 +101,491 @@
   </si>
   <si>
     <t>Rojahn TB, Vorstandlechner V, Krausgruber T, Bauer WM et al. Single-cell transcriptomics combined with interstitial fluid proteomics defines cell type-specific immune regulation in atopic dermatitis. J Allergy Clin Immunol 2020 Nov;146(5):1056-1069. PMID: 32344053. Rindler K, Krausgruber T, Thaler FM, Alkon N et al. Spontaneously Resolved Atopic Dermatitis Shows Melanocyte and Immune Cell Activation Distinct From Healthy Control Skin. Front Immunol 2021;12:630892. PMID: 33717163</t>
+  </si>
+  <si>
+    <t>He 2022</t>
+  </si>
+  <si>
+    <t>AD1</t>
+  </si>
+  <si>
+    <t>AD2</t>
+  </si>
+  <si>
+    <t>Healthy</t>
+  </si>
+  <si>
+    <t>Lesional</t>
+  </si>
+  <si>
+    <t>Non-Lesional</t>
+  </si>
+  <si>
+    <t>Number of cells</t>
+  </si>
+  <si>
+    <t>Sample ID</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>S1_LS </t>
+  </si>
+  <si>
+    <t>S2_LS</t>
+  </si>
+  <si>
+    <t>S3_NL</t>
+  </si>
+  <si>
+    <t>S4_H </t>
+  </si>
+  <si>
+    <t>S5_LS</t>
+  </si>
+  <si>
+    <t>S6_H </t>
+  </si>
+  <si>
+    <t>S7_LS</t>
+  </si>
+  <si>
+    <t>S8_H </t>
+  </si>
+  <si>
+    <t>S9_H </t>
+  </si>
+  <si>
+    <t>S10_H</t>
+  </si>
+  <si>
+    <t>S11_NL </t>
+  </si>
+  <si>
+    <t>S12_H</t>
+  </si>
+  <si>
+    <t>S13_H</t>
+  </si>
+  <si>
+    <t>S14_NL </t>
+  </si>
+  <si>
+    <t>S15_NL </t>
+  </si>
+  <si>
+    <t>S16_NL </t>
+  </si>
+  <si>
+    <t>S17_H</t>
+  </si>
+  <si>
+    <t>Sample_Title</t>
+  </si>
+  <si>
+    <t>GSM4430459</t>
+  </si>
+  <si>
+    <t>GSM4430460</t>
+  </si>
+  <si>
+    <t>GSM4430461</t>
+  </si>
+  <si>
+    <t>GSM4430462</t>
+  </si>
+  <si>
+    <t>GSM4430463</t>
+  </si>
+  <si>
+    <t>GSM4430464</t>
+  </si>
+  <si>
+    <t>GSM4430465</t>
+  </si>
+  <si>
+    <t>GSM4430466</t>
+  </si>
+  <si>
+    <t>GSM4430467</t>
+  </si>
+  <si>
+    <t>GSM4430468</t>
+  </si>
+  <si>
+    <t>GSM4430469</t>
+  </si>
+  <si>
+    <t>GSM4430470</t>
+  </si>
+  <si>
+    <t>GSM4430471</t>
+  </si>
+  <si>
+    <t>GSM4430472</t>
+  </si>
+  <si>
+    <t>GSM4430473</t>
+  </si>
+  <si>
+    <t>GSM4430474</t>
+  </si>
+  <si>
+    <t>GSM4430475</t>
+  </si>
+  <si>
+    <t>Tissue type</t>
+  </si>
+  <si>
+    <t>Disease</t>
+  </si>
+  <si>
+    <t>Atopic dermatitis</t>
+  </si>
+  <si>
+    <t>Sequencing Technology</t>
+  </si>
+  <si>
+    <t>3' Reagent Kit V2 (10x Genomics)</t>
+  </si>
+  <si>
+    <t>Institute</t>
+  </si>
+  <si>
+    <t>Icahn School of Medicine at Mt. Sinai, USA</t>
+  </si>
+  <si>
+    <t>He 2023</t>
+  </si>
+  <si>
+    <t>He 2024</t>
+  </si>
+  <si>
+    <t>He 2025</t>
+  </si>
+  <si>
+    <t>He 2026</t>
+  </si>
+  <si>
+    <t>He 2027</t>
+  </si>
+  <si>
+    <t>He 2028</t>
+  </si>
+  <si>
+    <t>He 2029</t>
+  </si>
+  <si>
+    <t>He 2030</t>
+  </si>
+  <si>
+    <t>He 2031</t>
+  </si>
+  <si>
+    <t>He 2032</t>
+  </si>
+  <si>
+    <t>He 2033</t>
+  </si>
+  <si>
+    <t>He 2034</t>
+  </si>
+  <si>
+    <t>Rindler_2021</t>
+  </si>
+  <si>
+    <t>AD20</t>
+  </si>
+  <si>
+    <t>AD21</t>
+  </si>
+  <si>
+    <t>AD24</t>
+  </si>
+  <si>
+    <t>AD25</t>
+  </si>
+  <si>
+    <t>GSM4932358</t>
+  </si>
+  <si>
+    <t>GSM4932359</t>
+  </si>
+  <si>
+    <t>GSM4932360</t>
+  </si>
+  <si>
+    <t>GSM4932361</t>
+  </si>
+  <si>
+    <t>Skin Suction blister</t>
+  </si>
+  <si>
+    <t>atopic comorbidities: Allergic rhinoconjunctivitis, asthma</t>
+  </si>
+  <si>
+    <t>version 3 (10x Genomics)</t>
+  </si>
+  <si>
+    <t>Medical University of Vienna</t>
+  </si>
+  <si>
+    <t>Alkon_2022</t>
+  </si>
+  <si>
+    <t>GSM5474333    </t>
+  </si>
+  <si>
+    <t>GSM5474334</t>
+  </si>
+  <si>
+    <t>GSM5474335</t>
+  </si>
+  <si>
+    <t>GSM5474336</t>
+  </si>
+  <si>
+    <t>GSM5474337</t>
+  </si>
+  <si>
+    <t>GSM5474338</t>
+  </si>
+  <si>
+    <t>GSM5474339</t>
+  </si>
+  <si>
+    <t>4 AD, 3(Healthy)</t>
+  </si>
+  <si>
+    <t>NHS1</t>
+  </si>
+  <si>
+    <t>NHS2</t>
+  </si>
+  <si>
+    <t>NHS3</t>
+  </si>
+  <si>
+    <t>AD3</t>
+  </si>
+  <si>
+    <t>AD4</t>
+  </si>
+  <si>
+    <t>AD5</t>
+  </si>
+  <si>
+    <t>Healthy Control</t>
+  </si>
+  <si>
+    <t>Skin Sheet</t>
+  </si>
+  <si>
+    <t>Skin Biopsies</t>
+  </si>
+  <si>
+    <t>Single Cell 3' v2 10X genomics</t>
+  </si>
+  <si>
+    <t>GEO ID</t>
+  </si>
+  <si>
+    <t>Rojahn_2020</t>
+  </si>
+  <si>
+    <t>GSM4653855 </t>
+  </si>
+  <si>
+    <t>GSM4653856</t>
+  </si>
+  <si>
+    <t>GSM4653857</t>
+  </si>
+  <si>
+    <t>GSM4653858</t>
+  </si>
+  <si>
+    <t>GSM4653859</t>
+  </si>
+  <si>
+    <t>GSM4653860</t>
+  </si>
+  <si>
+    <t>GSM4653861</t>
+  </si>
+  <si>
+    <t>GSM4653862</t>
+  </si>
+  <si>
+    <t>GSM4653863</t>
+  </si>
+  <si>
+    <t>GSM4653864</t>
+  </si>
+  <si>
+    <t>GSM4653865</t>
+  </si>
+  <si>
+    <t>GSM4653866</t>
+  </si>
+  <si>
+    <t>GSM4653867</t>
+  </si>
+  <si>
+    <t>GSM4653868</t>
+  </si>
+  <si>
+    <t>GSM4653869</t>
+  </si>
+  <si>
+    <t>AD6</t>
+  </si>
+  <si>
+    <t>AD7</t>
+  </si>
+  <si>
+    <t>AD8</t>
+  </si>
+  <si>
+    <t>HC1</t>
+  </si>
+  <si>
+    <t>HC2</t>
+  </si>
+  <si>
+    <t>HC3</t>
+  </si>
+  <si>
+    <t>HC4</t>
+  </si>
+  <si>
+    <t>HC5</t>
+  </si>
+  <si>
+    <t>HC6</t>
+  </si>
+  <si>
+    <t>HC7</t>
+  </si>
+  <si>
+    <t>Atopic Dermatitis</t>
+  </si>
+  <si>
+    <t>Healthy Control  </t>
+  </si>
+  <si>
+    <t>Skin Suction blister  </t>
+  </si>
+  <si>
+    <t>Skin Biopsy</t>
+  </si>
+  <si>
+    <t>GSE158432</t>
+  </si>
+  <si>
+    <t>Bangert_2021</t>
+  </si>
+  <si>
+    <t>patients with atopic  dermatitis (AD), who underwent short-term or long-term treatment with the IL-4Rα blocker  dupilumab</t>
+  </si>
+  <si>
+    <t>Bangert C, Rindler K, Krausgruber T, Alkon N et al. Persistence of mature dendritic cells, T(H)2A, and Tc2 cells characterize clinically resolved atopic dermatitis under IL-4Rα blockade. Sci Immunol 2021 Jan 22;6(55). PMID: 33483337</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE158432</t>
+  </si>
+  <si>
+    <t>GSM4800170    </t>
+  </si>
+  <si>
+    <t>GSM4800171</t>
+  </si>
+  <si>
+    <t>GSM4800172</t>
+  </si>
+  <si>
+    <t>GSM4800173</t>
+  </si>
+  <si>
+    <t>GSM4800174</t>
+  </si>
+  <si>
+    <t>GSM4800175</t>
+  </si>
+  <si>
+    <t>GSM4800176</t>
+  </si>
+  <si>
+    <t>GSM4800177</t>
+  </si>
+  <si>
+    <t>GSM4800178</t>
+  </si>
+  <si>
+    <t>GSM4800179</t>
+  </si>
+  <si>
+    <t>Dupilumab (16 weeks)       </t>
+  </si>
+  <si>
+    <t>Dupilumab (16 weeks)</t>
+  </si>
+  <si>
+    <t>Dupilumab (1 year)</t>
+  </si>
+  <si>
+    <t>untreated</t>
+  </si>
+  <si>
+    <t>AD10 </t>
+  </si>
+  <si>
+    <t>AD11</t>
+  </si>
+  <si>
+    <t>AD12</t>
+  </si>
+  <si>
+    <t>AD13</t>
+  </si>
+  <si>
+    <t>AD14</t>
+  </si>
+  <si>
+    <t>AD15</t>
+  </si>
+  <si>
+    <t>AD16</t>
+  </si>
+  <si>
+    <t>AD17</t>
+  </si>
+  <si>
+    <t>AD18</t>
+  </si>
+  <si>
+    <t>AD19</t>
+  </si>
+  <si>
+    <t>AD1  AD2  AD3  AD4  AD5  AD6  AD7  AD8  HC1  HC2  HC3  HC4  HC5  HC6  HC7 
+4846 3803 1819 3222 5628 5104 6246 5555   87  672 2662 2103  668 5455 9737</t>
+  </si>
+  <si>
+    <t>1054 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"># AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19  # 1054 1499 1570 4562 2976  489 1866 2478 1942  943 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -128,6 +599,23 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Menlo Regular"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,13 +638,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -492,16 +995,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722B7D77-8CB5-BC4B-A904-13AEF5D3DCF1}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.83203125" customWidth="1"/>
     <col min="4" max="4" width="23.6640625" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -518,13 +1022,19 @@
         <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -541,36 +1051,48 @@
         <v>18433</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
+        <v>106</v>
+      </c>
+      <c r="D3" s="1">
         <v>25034</v>
       </c>
       <c r="E3" s="1">
         <v>19195</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -587,37 +1109,1504 @@
         <v>18403</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="170">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="D5" s="1">
-        <v>76986</v>
+        <v>57607</v>
       </c>
       <c r="E5" s="1">
         <v>24984</v>
       </c>
       <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="1">
+        <v>19379</v>
+      </c>
+      <c r="F6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCE043ED-C4D8-754B-A1CC-084415222BF0}">
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="2" width="29" style="8" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="30.1640625" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="B2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="5">
+        <v>3904</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1836</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2084</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4745</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2328</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3320</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1546</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4431</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="5">
+        <v>6355</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1032</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6">
+        <v>2680</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="6">
+        <v>2409</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="6">
+        <v>258</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="6">
+        <v>815</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6">
+        <v>473</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="6">
+        <v>107</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1277</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="9">
+        <v>900</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="9">
+        <v>594</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="9">
+        <v>601</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="9">
+        <v>542</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="10">
+        <v>3663</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="10">
+        <v>2859</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="10">
+        <v>4653</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="10">
+        <v>3802</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="10">
+        <v>4084</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="10">
+        <v>3719</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="10">
+        <v>2254</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G6" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G30" s="10">
+        <v>4846</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="10">
+        <v>3803</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1819</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="10">
+        <v>3222</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" s="10">
+        <v>5628</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G35" s="10">
+        <v>5104</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G36" s="10">
+        <v>6246</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" s="10">
+        <v>5555</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="10">
+        <v>87</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="10">
+        <v>672</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G40" s="10">
+        <v>2662</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="10">
+        <v>2103</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" s="10">
+        <v>668</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="10">
+        <v>5455</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" s="10">
+        <v>9737</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G46" s="6">
+        <v>1499</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1570</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G48" s="6">
+        <v>4562</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G49" s="6">
+        <v>2976</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="6">
+        <v>489</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1866</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G52" s="6">
+        <v>2478</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G53" s="6">
+        <v>1942</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G54" s="6">
+        <v>943</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9451C90-E1DF-DF43-A968-45AE361FF447}">
+  <dimension ref="I24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="24" spans="9:9">
+      <c r="I24" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/StudyDetails.xlsx
+++ b/results/StudyDetails.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manjulat/Projects/Araichi/SkinDataAnalysis/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00AF491-C611-C246-8498-C9435D9D5DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A490D22C-3CA4-3340-B9DA-69F40642EEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11560" yWindow="660" windowWidth="22180" windowHeight="16680" activeTab="1" xr2:uid="{25722A3C-8689-2743-954C-0104D0233038}"/>
+    <workbookView xWindow="1820" yWindow="660" windowWidth="15680" windowHeight="16680" activeTab="1" xr2:uid="{25722A3C-8689-2743-954C-0104D0233038}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="176">
   <si>
     <t>Study</t>
   </si>
@@ -46,9 +46,6 @@
     <t>NumberofSamples</t>
   </si>
   <si>
-    <t>Condition</t>
-  </si>
-  <si>
     <t>NumberofCells</t>
   </si>
   <si>
@@ -58,15 +55,9 @@
     <t>NumberofGenes</t>
   </si>
   <si>
-    <t>5 Non-Lesional, 4 Lesional,  8 Healthy</t>
-  </si>
-  <si>
     <t>GSE162054</t>
   </si>
   <si>
-    <t>All AD, AD20(900) AD21(594) AD24(601) AD25(542)</t>
-  </si>
-  <si>
     <t>GSE153760</t>
   </si>
   <si>
@@ -100,9 +91,6 @@
     <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE153760</t>
   </si>
   <si>
-    <t>Rojahn TB, Vorstandlechner V, Krausgruber T, Bauer WM et al. Single-cell transcriptomics combined with interstitial fluid proteomics defines cell type-specific immune regulation in atopic dermatitis. J Allergy Clin Immunol 2020 Nov;146(5):1056-1069. PMID: 32344053. Rindler K, Krausgruber T, Thaler FM, Alkon N et al. Spontaneously Resolved Atopic Dermatitis Shows Melanocyte and Immune Cell Activation Distinct From Healthy Control Skin. Front Immunol 2021;12:630892. PMID: 33717163</t>
-  </si>
-  <si>
     <t>He 2022</t>
   </si>
   <si>
@@ -250,9 +238,6 @@
     <t>Sequencing Technology</t>
   </si>
   <si>
-    <t>3' Reagent Kit V2 (10x Genomics)</t>
-  </si>
-  <si>
     <t>Institute</t>
   </si>
   <si>
@@ -358,9 +343,6 @@
     <t>GSM5474339</t>
   </si>
   <si>
-    <t>4 AD, 3(Healthy)</t>
-  </si>
-  <si>
     <t>NHS1</t>
   </si>
   <si>
@@ -388,9 +370,6 @@
     <t>Skin Biopsies</t>
   </si>
   <si>
-    <t>Single Cell 3' v2 10X genomics</t>
-  </si>
-  <si>
     <t>GEO ID</t>
   </si>
   <si>
@@ -571,14 +550,22 @@
     <t>AD19</t>
   </si>
   <si>
-    <t>AD1  AD2  AD3  AD4  AD5  AD6  AD7  AD8  HC1  HC2  HC3  HC4  HC5  HC6  HC7 
-4846 3803 1819 3222 5628 5104 6246 5555   87  672 2662 2103  668 5455 9737</t>
-  </si>
-  <si>
     <t>1054 </t>
   </si>
   <si>
-    <t xml:space="preserve"># AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19  # 1054 1499 1570 4562 2976  489 1866 2478 1942  943 </t>
+    <t xml:space="preserve">10 AD </t>
+  </si>
+  <si>
+    <t>Non-lesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rojahn TB, Vorstandlechner V, Krausgruber T, Bauer WM et al. Single-cell transcriptomics combined with interstitial fluid proteomics defines cell type-specific immune regulation in atopic dermatitis. J Allergy Clin Immunol 2020 Nov;146(5):1056-1069. PMID: 32344053. </t>
+  </si>
+  <si>
+    <t>3' v2 (10x Genomics)</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -638,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -652,15 +639,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -995,17 +977,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722B7D77-8CB5-BC4B-A904-13AEF5D3DCF1}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="3" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22">
+    <row r="1" spans="1:11" ht="22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1013,161 +995,186 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>4</v>
       </c>
       <c r="B2">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1">
         <v>39600</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>18433</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1">
         <v>25034</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>19195</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1">
         <v>2637</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>18403</v>
       </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="170">
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5" s="2">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="1">
         <v>57607</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>24984</v>
       </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B6">
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="1">
+        <v>171</v>
+      </c>
+      <c r="F6" s="1">
         <v>19379</v>
       </c>
-      <c r="F6" t="s">
-        <v>152</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>151</v>
+      <c r="H6" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1187,7 @@
   <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="29" style="8" customWidth="1"/>
+    <col min="1" max="2" width="29" style="7" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
     <col min="6" max="6" width="30.1640625" customWidth="1"/>
@@ -1188,1410 +1195,1410 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="B1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="8" t="s">
+      <c r="E2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="G2" s="5">
         <v>3904</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>30</v>
+      <c r="H2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="G3" s="5">
         <v>1836</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>30</v>
+      <c r="H3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>4</v>
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>26</v>
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
       </c>
       <c r="G4" s="5">
         <v>2084</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
       </c>
       <c r="G5" s="5">
         <v>4745</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>30</v>
+      <c r="H5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="G6" s="5">
         <v>2328</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>30</v>
+      <c r="H6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>4</v>
+      <c r="A7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
       </c>
       <c r="G7" s="5">
         <v>3320</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>30</v>
+      <c r="H7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
+      <c r="A8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>25</v>
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
       </c>
       <c r="G8" s="5">
         <v>1546</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>30</v>
+      <c r="H8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>4</v>
+      <c r="A9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
       </c>
       <c r="G9" s="5">
         <v>4431</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>30</v>
+      <c r="H9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>4</v>
+      <c r="A10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
       </c>
       <c r="G10" s="5">
         <v>6355</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>30</v>
+      <c r="H10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>4</v>
+      <c r="A11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
       </c>
       <c r="G11" s="6">
         <v>1032</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>30</v>
+      <c r="H11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>4</v>
+      <c r="A12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>26</v>
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
       </c>
       <c r="G12" s="6">
         <v>2680</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>30</v>
+      <c r="H12" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>4</v>
+      <c r="A13" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
       </c>
       <c r="G13" s="6">
         <v>2409</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>30</v>
+      <c r="H13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>4</v>
+      <c r="A14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="6">
         <v>258</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>30</v>
+      <c r="H14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>4</v>
+      <c r="A15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>26</v>
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
       </c>
       <c r="G15" s="6">
         <v>815</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>30</v>
+      <c r="H15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>4</v>
+      <c r="A16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>26</v>
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
       </c>
       <c r="G16" s="6">
         <v>473</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>30</v>
+      <c r="H16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>4</v>
+      <c r="A17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>26</v>
+      <c r="F17" t="s">
+        <v>22</v>
       </c>
       <c r="G17" s="6">
         <v>107</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>30</v>
+      <c r="H17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>4</v>
+      <c r="A18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
       </c>
       <c r="G18" s="6">
         <v>1277</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>30</v>
+      <c r="H18" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="D19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="8">
+        <v>900</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="8">
+        <v>594</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="8">
+        <v>601</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="8">
+        <v>542</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G19" s="9">
-        <v>900</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="D23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G23" s="8">
+        <v>3663</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="D24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="8">
+        <v>2859</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="C25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="8">
+        <v>4653</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="8">
+        <v>3802</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="8">
+        <v>4084</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="8">
+        <v>3719</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="8">
+        <v>2254</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="8">
+        <v>4846</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="8">
+        <v>3803</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1819</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="8">
+        <v>3222</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="8">
+        <v>5628</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" s="8">
+        <v>5104</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G36" s="8">
+        <v>6246</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G37" s="8">
+        <v>5555</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G38" s="8">
         <v>87</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="9">
-        <v>594</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="9">
-        <v>601</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="H38" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="9">
-        <v>542</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="G39" s="8">
+        <v>672</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G23" s="10">
-        <v>3663</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="10">
-        <v>2859</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="10">
-        <v>4653</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G26" s="10">
-        <v>3802</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G27" s="10">
-        <v>4084</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="F40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G40" s="8">
+        <v>2662</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G28" s="10">
-        <v>3719</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G29" s="10">
-        <v>2254</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G30" s="10">
-        <v>4846</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G31" s="10">
-        <v>3803</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G32" s="10">
-        <v>1819</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="B41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" s="8">
+        <v>2103</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G33" s="10">
-        <v>3222</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G34" s="10">
-        <v>5628</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="4" t="s">
+      <c r="B42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G35" s="10">
-        <v>5104</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="E42" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G42" s="8">
+        <v>668</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D43" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G36" s="10">
-        <v>6246</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="E43" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" s="8">
+        <v>5455</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G37" s="10">
-        <v>5555</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G38" s="10">
-        <v>87</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" s="10">
-        <v>672</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G40" s="10">
-        <v>2662</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="E44" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41" s="10">
-        <v>2103</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G42" s="10">
-        <v>668</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G43" s="10">
-        <v>5455</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G44" s="10">
+      <c r="G44" s="8">
         <v>9737</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G46" s="6">
         <v>1499</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="D47" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G47" s="6">
         <v>1570</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="D48" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G48" s="6">
         <v>4562</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G49" s="6">
         <v>2976</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G50" s="6">
         <v>489</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G51" s="6">
         <v>1866</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G52" s="6">
         <v>2478</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G53" s="6">
         <v>1942</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G54" s="6">
         <v>943</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/results/StudyDetails.xlsx
+++ b/results/StudyDetails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manjulat/Projects/Araichi/SkinDataAnalysis/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A490D22C-3CA4-3340-B9DA-69F40642EEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E64460C-E1CA-734E-BE98-CB7473DA012C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1820" yWindow="660" windowWidth="15680" windowHeight="16680" activeTab="1" xr2:uid="{25722A3C-8689-2743-954C-0104D0233038}"/>
+    <workbookView xWindow="1820" yWindow="660" windowWidth="23540" windowHeight="16680" xr2:uid="{25722A3C-8689-2743-954C-0104D0233038}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="175">
   <si>
     <t>Study</t>
   </si>
@@ -313,9 +313,6 @@
     <t>atopic comorbidities: Allergic rhinoconjunctivitis, asthma</t>
   </si>
   <si>
-    <t>version 3 (10x Genomics)</t>
-  </si>
-  <si>
     <t>Medical University of Vienna</t>
   </si>
   <si>
@@ -553,9 +550,6 @@
     <t>1054 </t>
   </si>
   <si>
-    <t xml:space="preserve">10 AD </t>
-  </si>
-  <si>
     <t>Non-lesional</t>
   </si>
   <si>
@@ -566,6 +560,9 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>3' v3 (10x Genomics)</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +998,7 @@
         <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2</v>
@@ -1051,7 +1048,7 @@
         <v>11</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>67</v>
@@ -1083,10 +1080,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1112,10 +1109,10 @@
         <v>15</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1142,39 +1139,42 @@
         <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>171</v>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="F6" s="1">
         <v>19379</v>
       </c>
+      <c r="G6" s="1">
+        <v>22176</v>
+      </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
         <v>24</v>
@@ -1768,22 +1768,22 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="G23" s="8">
         <v>3663</v>
@@ -1794,22 +1794,22 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="G24" s="8">
         <v>2859</v>
@@ -1820,22 +1820,22 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="G25" s="8">
         <v>4653</v>
@@ -1846,13 +1846,13 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>19</v>
@@ -1861,7 +1861,7 @@
         <v>64</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G26" s="8">
         <v>3802</v>
@@ -1872,22 +1872,22 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>64</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G27" s="8">
         <v>4084</v>
@@ -1898,22 +1898,22 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G28" s="8">
         <v>3719</v>
@@ -1924,22 +1924,22 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G29" s="8">
         <v>2254</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G30" s="8">
         <v>4846</v>
@@ -1976,19 +1976,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>89</v>
@@ -2002,19 +2002,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>89</v>
@@ -2028,19 +2028,19 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>89</v>
@@ -2054,22 +2054,22 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G34" s="8">
         <v>5628</v>
@@ -2080,22 +2080,22 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G35" s="8">
         <v>5104</v>
@@ -2106,22 +2106,22 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G36" s="8">
         <v>6246</v>
@@ -2132,22 +2132,22 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G37" s="8">
         <v>5555</v>
@@ -2158,19 +2158,19 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>89</v>
@@ -2184,19 +2184,19 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>89</v>
@@ -2210,19 +2210,19 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>89</v>
@@ -2236,19 +2236,19 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>89</v>
@@ -2262,19 +2262,19 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>89</v>
@@ -2288,22 +2288,22 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G43" s="8">
         <v>5455</v>
@@ -2314,22 +2314,22 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G44" s="8">
         <v>9737</v>
@@ -2340,48 +2340,48 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>89</v>
@@ -2390,24 +2390,24 @@
         <v>1499</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>89</v>
@@ -2416,24 +2416,24 @@
         <v>1570</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>89</v>
@@ -2442,24 +2442,24 @@
         <v>4562</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>89</v>
@@ -2468,24 +2468,24 @@
         <v>2976</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>89</v>
@@ -2494,24 +2494,24 @@
         <v>489</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>89</v>
@@ -2520,24 +2520,24 @@
         <v>1866</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>89</v>
@@ -2546,24 +2546,24 @@
         <v>2478</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>89</v>
@@ -2572,24 +2572,24 @@
         <v>1942</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>89</v>
@@ -2598,7 +2598,7 @@
         <v>943</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
